--- a/12628972.xlsx
+++ b/12628972.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776 Workbook\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A24871-5B06-4BE2-86B9-4BB6CB4536DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E3AC37-BC61-4C2F-BAA8-1EA338FCBCC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -188,9 +188,6 @@
   </si>
   <si>
     <t>Satisfied</t>
-  </si>
-  <si>
-    <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
   </si>
   <si>
     <t>5. GOOD PRACTICE</t>
@@ -841,7 +838,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
@@ -911,7 +908,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -928,7 +925,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -936,7 +933,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1002,7 +999,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>46276</v>
       </c>
@@ -1042,11 +1039,9 @@
         <v>50</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>51</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
@@ -1082,13 +1077,13 @@
         <v>660</v>
       </c>
       <c r="K7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L7" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="M7" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N7" s="17"/>
     </row>
@@ -1129,10 +1124,10 @@
         <v>49</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N8" s="17"/>
     </row>
@@ -1170,13 +1165,13 @@
         <v>595</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L9" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N9" s="17"/>
     </row>
@@ -1214,13 +1209,13 @@
         <v>490</v>
       </c>
       <c r="K10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="16" t="s">
         <v>61</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>62</v>
       </c>
       <c r="N10" s="17"/>
     </row>
@@ -1264,96 +1259,184 @@
         <v>50</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B12" s="14">
+        <v>480</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>110</v>
+      </c>
+      <c r="E12" s="14">
+        <v>70</v>
+      </c>
+      <c r="F12" s="14">
+        <v>150</v>
+      </c>
+      <c r="G12" s="14">
+        <v>3</v>
+      </c>
+      <c r="H12" s="14">
+        <v>60</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B13" s="14">
+        <v>375</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>50</v>
+      </c>
+      <c r="E13" s="14">
+        <v>45</v>
+      </c>
+      <c r="F13" s="14">
+        <v>250</v>
+      </c>
+      <c r="G13" s="14">
+        <v>5</v>
+      </c>
+      <c r="H13" s="14">
+        <v>45</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>765</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>675</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B14" s="14">
+        <v>500</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>70</v>
+      </c>
+      <c r="E14" s="14">
+        <v>80</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>80</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>710</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B15" s="14">
+        <v>477</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>115</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>110</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>822</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>618</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628972.xlsx
+++ b/12628972.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E3AC37-BC61-4C2F-BAA8-1EA338FCBCC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138A3738-F4E5-4C56-99D7-65DEF7DE8D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1440,25 +1440,47 @@
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B16" s="14">
+        <v>360</v>
+      </c>
+      <c r="C16" s="14">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>150</v>
+      </c>
+      <c r="E16" s="14">
+        <v>90</v>
+      </c>
+      <c r="F16" s="14">
+        <v>200</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>75</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>895</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>545</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628972.xlsx
+++ b/12628972.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138A3738-F4E5-4C56-99D7-65DEF7DE8D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2DFE73-7D94-46BF-A3CD-474EEF49B34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1484,25 +1484,47 @@
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B17" s="14">
+        <v>380</v>
+      </c>
+      <c r="C17" s="14">
+        <v>30</v>
+      </c>
+      <c r="D17" s="14">
+        <v>100</v>
+      </c>
+      <c r="E17" s="14">
+        <v>75</v>
+      </c>
+      <c r="F17" s="14">
+        <v>350</v>
+      </c>
+      <c r="G17" s="14">
+        <v>7</v>
+      </c>
+      <c r="H17" s="14">
+        <v>45</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628972.xlsx
+++ b/12628972.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2DFE73-7D94-46BF-A3CD-474EEF49B34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C02B922-AC73-4DF3-82B2-F43324E4A2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1528,25 +1528,47 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B18" s="14">
+        <v>410</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>100</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>300</v>
+      </c>
+      <c r="G18" s="14">
+        <v>5</v>
+      </c>
+      <c r="H18" s="14">
+        <v>30</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628972.xlsx
+++ b/12628972.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C02B922-AC73-4DF3-82B2-F43324E4A2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8CC4F7-7EA3-4F89-97AE-1A87F5F253C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1572,25 +1572,47 @@
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B19" s="14">
+        <v>400</v>
+      </c>
+      <c r="C19" s="14">
+        <v>20</v>
+      </c>
+      <c r="D19" s="14">
+        <v>85</v>
+      </c>
+      <c r="E19" s="14">
+        <v>110</v>
+      </c>
+      <c r="F19" s="14">
+        <v>100</v>
+      </c>
+      <c r="G19" s="14">
+        <v>2</v>
+      </c>
+      <c r="H19" s="14">
+        <v>40</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>755</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>685</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">

--- a/12628972.xlsx
+++ b/12628972.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8CC4F7-7EA3-4F89-97AE-1A87F5F253C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F5A4A3-9BD7-4FEF-99F8-596F2B8585DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1616,25 +1616,47 @@
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B20" s="14">
+        <v>360</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>135</v>
+      </c>
+      <c r="E20" s="14">
+        <v>105</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14">
+        <v>80</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
